--- a/data/seed/portfolio/L-2025-3032/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-3032/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I203"/>
+  <dimension ref="A1:I184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -560,31 +560,31 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>3751000</v>
+        <v>19055000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Shodlik Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>330013963</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000066780292001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1118 01.07.2026, QQS bilan</t>
+          <t>Shartnoma №131/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -601,38 +601,38 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>1877000</v>
+        <v>4834000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mehnat Qurilish MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>208913806</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000390726349001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2666</t>
+          <t>SHARTNOMA №267/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,31 +642,31 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>2750000</v>
+        <v>3514000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5439 от 02.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №3/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -683,38 +683,38 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>2641000</v>
+        <v>1715000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2993 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №3330 от 02.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -722,33 +722,33 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>13464000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>7767000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Toshkent Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>337093444</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000399671039001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5788</t>
+          <t>Yetkazilga tovar uchun to'lov h/f №6274</t>
         </is>
       </c>
     </row>
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>23491000</v>
+        <v>6960000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zafar Avto Savdo MChJ</t>
+          <t>Oltin Vodiy Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>243624254</t>
+          <t>302194098</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000998814756001</t>
+          <t>20208000376079344001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №209/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, h/f №3093 06.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -806,31 +806,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>10327000</v>
+        <v>1696000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8230 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №8815 06.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -845,33 +845,28 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>8848000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>19107000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qarshi Non MChJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>376646629</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000922620047001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9376</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
@@ -886,40 +881,40 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>2087000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>35692000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>241356725</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000380253078001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9217</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №113/26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -927,40 +922,40 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>4249000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>14104000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kamalak Plastik AJ</t>
+          <t>Toshkent Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>235680841</t>
+          <t>337093444</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000008619306001</t>
+          <t>20208000399671039001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №36/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №69/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,40 +963,40 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>5064000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>1597000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №94/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5924</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1009,40 +1004,40 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>13072000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>8854000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Toshkent Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>337093444</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000399671039001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №133/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5717 08.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1050,35 +1045,40 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>19107000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>5799000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Oltin Vodiy Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №4789</t>
+          <t>Shartnoma №65/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1088,38 +1088,38 @@
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>2153000</v>
+        <v>5723000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7616 07.07.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7507 09.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1129,38 +1129,38 @@
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>2111000</v>
+        <v>3464000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2933</t>
+          <t>Оплата по с/ф №4124 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,40 +1168,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>2035000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>2183000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>358326321</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000698368861001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №105/26, QQS 12%</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1209,40 +1209,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>2183000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>7203000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>270068797</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000136675861001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BINO IJARASI UCHUN TO'LOV IYUL</t>
+          <t>Оплата за продукцию по дог. №277/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,33 +1250,33 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>28252000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>1915000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №79/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2210 10.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1291,40 +1291,35 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>53467000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>14900000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>359135425</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3032)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>16307000251139996417</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3246 10.07.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-3032 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1334,38 +1329,38 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>8309000</v>
+        <v>15037000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №237/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №9926 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1373,40 +1368,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>4728000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>8746000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №141/26</t>
+          <t>Предоплата за товар по договору №200/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1414,28 +1409,33 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>14900000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>3346000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3032)</t>
+          <t>Oltin Vodiy Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>16307000251139996417</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3032 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Shartnoma №36/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -1452,31 +1452,31 @@
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>14073000</v>
+        <v>1873000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №113/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7897 13.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1493,31 +1493,31 @@
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>8192000</v>
+        <v>1180000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3970</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8651 13.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1533,32 +1533,32 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3066000</v>
+        <v>8328000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №255/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №266/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1574,22 +1574,22 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>5098000</v>
+        <v>19443000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Mehnat Savdo MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>337257395</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000014759122001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1599,14 +1599,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4269</t>
+          <t>Tovarlar uchun to'lov h/f №3289</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1614,33 +1614,33 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>16612000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>31388000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №139/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №138/26</t>
         </is>
       </c>
     </row>
@@ -1657,31 +1657,31 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>9479000</v>
+        <v>6076000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Shartnoma №210/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №164/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -1698,31 +1698,31 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>3351000</v>
+        <v>1496000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2669</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5511 14.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1739,38 +1739,38 @@
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>2074000</v>
+        <v>1323000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9852</t>
+          <t>Оплата за продукцию по договору №275/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1778,40 +1778,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>2605000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>3662000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Toshkent Ip-Kalava XK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>364662999</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000262004770001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8382</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,14 +1845,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1861,39 +1861,39 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>3438000</v>
+        <v>2605000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Guliston Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>366300139</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000360667802001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №242/26</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1901,40 +1901,40 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>29159000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>3096000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ilhom Qurilish MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>311312328</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000554060146001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №84</t>
+          <t>Shartnoma №180/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1942,40 +1942,40 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>11600000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>24626000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Mehnat Savdo MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>337257395</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000014759122001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №243/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №4078</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1983,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>2745000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>47135000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>241356725</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000380253078001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5310 15.07.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №41/26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2026,31 +2026,31 @@
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>1566000</v>
+        <v>19314000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Shartnoma №74/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №52/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -2067,21 +2067,21 @@
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>12532000</v>
+        <v>7523000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1614</t>
+          <t>Shartnoma №214/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -2108,31 +2108,31 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>3781000</v>
+        <v>2821000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Oydin Non AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>312208384</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000596651553001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Shartnoma №296/26 bo'icha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №100/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -2149,31 +2149,31 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>2088000</v>
+        <v>2022000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Shartnoma №241/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4464</t>
         </is>
       </c>
     </row>
@@ -2190,31 +2190,31 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>1651000</v>
+        <v>1755000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Toshkent Ip-Kalava XK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>364662999</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000262004770001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №270/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №200/26 от 20.07.2026</t>
         </is>
       </c>
     </row>
@@ -2229,33 +2229,33 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>1532000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>21537000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Xiva Mebel AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>339941199</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000807658318001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3891</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №6/26</t>
         </is>
       </c>
     </row>
@@ -2271,39 +2271,39 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>7561000</v>
+        <v>28936000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Afrosiyob Moy AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>383300872</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000184955062001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №595</t>
+          <t>Оплата за сырье по договору №130/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,33 +2311,33 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>21711000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>1619000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Guliston Qog'oz MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>366300139</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000360667802001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №81/26</t>
+          <t>Shartnoma №299/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>3655000</v>
+        <v>3592000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
@@ -2378,14 +2378,14 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2393,40 +2393,40 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>3987000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>1635000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Ilhom Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>282309911</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000484048031001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1294</t>
+          <t>Shartnoma №140/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2436,38 +2436,38 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>8043000</v>
+        <v>1756000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6664 27.07.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №170/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2475,40 +2475,40 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>6791000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>8657000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Mehnat Savdo MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>337257395</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000014759122001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1541 27.07.2026, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartn. №286/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2516,33 +2516,33 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>5251000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>13995000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Shartnoma №55/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №179/26</t>
         </is>
       </c>
     </row>
@@ -2559,21 +2559,21 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>4075000</v>
+        <v>22457000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Denov Plastik MChJ</t>
+          <t>Toshkent Ip-Kalava XK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>280939580</t>
+          <t>364662999</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000543058880001</t>
+          <t>20208000262004770001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Shartnoma №200/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №38/26 от 27.07.2026</t>
         </is>
       </c>
     </row>
@@ -2600,31 +2600,31 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>1329000</v>
+        <v>14698000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №228/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, h/f №2730 27.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -2639,40 +2639,40 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>1364000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>3523000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000408297732001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Shartnoma №288/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2682,38 +2682,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>7735000</v>
+        <v>2826000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №228/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, h/f №4542 27.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,38 +2723,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>2721000</v>
+        <v>2565000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №279/26, QQS 12%</t>
+          <t>Shartnoma №57/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2762,33 +2762,33 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>2605000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>1364000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000944796837001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Shartnoma №237/26 bo'yicha oldindan to'lov</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
     </row>
@@ -2803,40 +2803,40 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>5123000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>4209000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №182/26 от 28.07.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lv, shartnoma №132/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2844,33 +2844,33 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>17333000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>11401000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>241356725</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000380253078001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7152</t>
+          <t>Tovarlar uchun to'lov h/f №4003</t>
         </is>
       </c>
     </row>
@@ -2887,38 +2887,38 @@
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>7402000</v>
+        <v>3588000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №100/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2102 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2926,40 +2926,40 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>55892000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>3586000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №1488</t>
+          <t>Mahsulot uchun to'lov, shartn. №37/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2969,38 +2969,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>8926000</v>
+        <v>63372000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>369409395</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000561422442001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №282/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1829</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3008,40 +3008,35 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>5167000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Qarshi Non MChJ</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>376646629</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000922620047001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6399</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3051,21 +3046,21 @@
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>1769000</v>
+        <v>7007000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3075,14 +3070,14 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Shartnoma №38/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №169/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3092,38 +3087,38 @@
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>1396000</v>
+        <v>3334000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2102</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4774</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3131,40 +3126,40 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>47197000</v>
-      </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n">
+        <v>3075000</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kamalak Plastik AJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>235680841</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000008619306001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №99/26</t>
+          <t>Tovar uchun to'lov, h/f №9040 03.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3174,38 +3169,38 @@
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>7109000</v>
+        <v>1849000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9724 от 31.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8936</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3215,38 +3210,38 @@
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>1820000</v>
+        <v>1633000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8389 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Mahsulot uchun to'lov, shartnoma №87/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3254,35 +3249,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>2081000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Oltin Vodiy Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5970</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3290,40 +3290,35 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>4849000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>18742000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>347370934</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №190/26, QQS 12%</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3331,40 +3326,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>3230000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>3144000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>241356725</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000380253078001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Shartnoma №246/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №2/26</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3372,40 +3367,40 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>2256000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>10264000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5525</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №54/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3415,38 +3410,38 @@
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>2014000</v>
+        <v>26971000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Sharq Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>346984504</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000881311841001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №757 03.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №92/26 от 07.08.2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3456,38 +3451,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>1744000</v>
+        <v>2578000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Toshkent Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>337093444</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000399671039001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1781</t>
+          <t>Оплата за продукцию по договору №83/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3495,40 +3490,40 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>4832000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>3552000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kamalak Plastik AJ</t>
+          <t>Toshkent Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>235680841</t>
+          <t>337093444</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000008619306001</t>
+          <t>20208000399671039001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №5530</t>
+          <t>Mahsulot uchun to'lov, shartnoma №141/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3536,40 +3531,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>7104000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>2977000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №8169</t>
+          <t>Mahsulot uchun to'lov, shartn. №97/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3577,40 +3572,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>2559000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>2141000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>358326321</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000698368861001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Shartnoma №153/26 bo'yicha oldindan to'lov</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3618,40 +3613,35 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>12841000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>14900000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>359135425</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3032)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>16307000251139996417</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9172 05.08.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-3032 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3661,38 +3651,38 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>1408000</v>
+        <v>2290000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Bog'ishamol Metall Servis XK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>293958025</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000305888016001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №5949</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №117/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3701,39 +3691,39 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>4184000</v>
+        <v>5640000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №54/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartn. №124/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3741,23 +3731,23 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>4996000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>8200000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3767,14 +3757,14 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №2/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №75/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3783,17 +3773,22 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>18742000</v>
+        <v>3527000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>241356725</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000380253078001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3803,14 +3798,14 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №4920</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №217/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3820,38 +3815,38 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>4162000</v>
+        <v>4031000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №200/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №7895 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3861,38 +3856,38 @@
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>1726000</v>
+        <v>2597000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Toshkent Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>337093444</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000399671039001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №113/26 от 07.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №183/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3902,38 +3897,38 @@
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>1210000</v>
+        <v>1845000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Shartnoma №168/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №9820 от 14.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3941,40 +3936,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>3282000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>1763000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Toshkent Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>337093444</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000399671039001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №32/26</t>
+          <t>Shartnoma №158/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3982,40 +3977,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>3418000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>2556000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1660</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4023,40 +4018,40 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>2403000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>2556000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2707</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4064,40 +4059,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>1796000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>9265000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Qarshi Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>227959841</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000618750957001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №41/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №162/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4105,40 +4100,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>1105000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>15479000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Shartnoma №95/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №220/26</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4146,40 +4141,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>2141000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>7167000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>270068797</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000136675861001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №76/25</t>
+          <t>Предоплата за товар по договору №145/26 от 17.08.2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4187,35 +4182,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>14900000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>6152000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3032)</t>
+          <t>Oltin Vodiy Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>16307000251139996417</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3032 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8674</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4223,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>2441000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>5011000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Toshkent Ip-Kalava XK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>364662999</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000262004770001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №134/26</t>
+          <t>Оплата за товар по счет-фактуре №2241 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4266,38 +4266,38 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>5724000</v>
+        <v>2251000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Qarshi Non MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>376646629</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000922620047001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Shartnoma №135/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №17/26 QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4307,38 +4307,38 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>1248000</v>
+        <v>2100000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Denov Plastik MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>280939580</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000543058880001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №8297</t>
+          <t>Mahsulot uchun to'lov, shartnoma №152/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4346,23 +4346,23 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>3214000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>1788000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4372,14 +4372,14 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №217/26, QQS bilan</t>
+          <t>Shartnoma №148/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4388,39 +4388,39 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>3507000</v>
+        <v>4644000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>241356725</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000380253078001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №220/26</t>
+          <t>Оплата за транспортные услуги по договору №203/26</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4428,40 +4428,40 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>23209000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>3270000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Durdona Sut Mahsulotlari MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>395833008</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000241849550001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №162/26, QQS bilan</t>
+          <t>Shartnoma №172/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,40 +4469,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>2904000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>6981000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3509 17.08.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №180/26</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4510,40 +4510,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>2727000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>4742000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №656 17.08.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №19/26</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4551,40 +4551,40 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>2421000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>6045000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>241356725</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000380253078001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9308 17.08.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №59/26</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4594,38 +4594,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>2296000</v>
+        <v>17156000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №88/26, QQS 12%</t>
+          <t>Shartnoma №180/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4635,38 +4635,38 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>1192000</v>
+        <v>7227000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2254 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №182/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4674,40 +4674,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>2556000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>3027000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №631</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>2556000</v>
+        <v>3522000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
@@ -4741,14 +4741,14 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4756,23 +4756,23 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>18199000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>77616000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Oydin Non AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>312208384</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000596651553001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4782,14 +4782,14 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №203/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6806</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4797,40 +4797,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>2176000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>4697000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №180/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2244</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4838,40 +4838,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>24576000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>2654000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №124/26, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4803 24.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4881,38 +4881,38 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>1061000</v>
+        <v>2607000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Shartnoma №231/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2504</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4920,40 +4920,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>10713000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>2131000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №19/26</t>
+          <t>Shartnoma №234/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4962,39 +4962,39 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>12279000</v>
+        <v>1338000</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000944796837001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №59/26</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5002,40 +5002,40 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>60795000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>3065000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4354</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №200/26</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5043,40 +5043,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>2368000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>5067000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Shartnoma №15/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №277/26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5084,23 +5084,23 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>1757000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>33533000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Afrosiyob Moy AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>383300872</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000184955062001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5110,14 +5110,14 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №280/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №4665</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5126,39 +5126,39 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>71747000</v>
+        <v>103652000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>241356725</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000380253078001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9749</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №5/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5168,38 +5168,38 @@
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>18249000</v>
+        <v>31096000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №74/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №5404 от 25.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5209,21 +5209,21 @@
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>5971000</v>
+        <v>9234000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Qarshi Non MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>376646629</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000922620047001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5233,14 +5233,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Shartnoma №139/26 bo'yicha oldindan to'lov</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №3487</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5250,38 +5250,38 @@
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>3895000</v>
+        <v>3500000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4384 24.08.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5385</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5291,38 +5291,38 @@
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>2048000</v>
+        <v>2539000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Lazzat Qurilish AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>312035458</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000819013163001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9324 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №8770 25.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5332,38 +5332,38 @@
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>1229000</v>
+        <v>1564000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3909 24.08.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №173/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5372,39 +5372,39 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>2121000</v>
+        <v>32324000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Guliston Qog'oz MChJ</t>
+          <t>Xiva Mebel AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>366300139</t>
+          <t>339941199</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000360667802001</t>
+          <t>20208000807658318001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4665</t>
+          <t>Tovarlar uchun to'lov h/f №6649</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5412,40 +5412,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>3572000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>9059000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Shartnoma №243/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5453,40 +5453,40 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>5758000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>4016000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Toshkent Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>337093444</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000399671039001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №277/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №165/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5494,40 +5494,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>10268000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>6176000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Oydin Non AJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>312208384</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>20208000596651553001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №200/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5787</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5535,40 +5535,40 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>22373000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>3687000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №5/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №28/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5578,38 +5578,38 @@
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>2764000</v>
+        <v>1960000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Toshkent Ip-Kalava XK</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>364662999</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000262004770001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №1346 25.08.2026, QQS BILAN</t>
+          <t>Mahsulot uchun to'lov, shartnoma №206/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5618,39 +5618,34 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>3903000</v>
+        <v>300000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona XK</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>336433225</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000853008516001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6649</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5660,38 +5655,38 @@
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>46908000</v>
+        <v>4407000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Lazzat Qurilish AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>312035458</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000819013163001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №1803 26.08.2026, QQS BILAN</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7483</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5699,40 +5694,40 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>6413000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>7563000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №219/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6400</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5740,40 +5735,40 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>1338000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>22939000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000408297732001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за продукцию по дог. №85/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5783,38 +5778,38 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>5094000</v>
+        <v>14000000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Oydin Non AJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>312208384</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000596651553001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SHARTNOMA №29/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №502</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5824,38 +5819,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>3314000</v>
+        <v>6015000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Shartnoma №194/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3453 03.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5865,38 +5860,38 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>2359000</v>
+        <v>14494000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4320 за поставленный товар</t>
+          <t>Shartnoma №233/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5906,38 +5901,38 @@
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>1421000</v>
+        <v>8392000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3527</t>
+          <t>Shartnoma №146/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5945,40 +5940,35 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>52502000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>16907000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Zafar Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>243624254</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000998814756001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8087 31.08.2026, QQS bilan</t>
+          <t>Avgust oyi uchun ish haqi, reestr №7839</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5988,38 +5978,38 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>7114000</v>
+        <v>44323000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Toshkent Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>337093444</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000399671039001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7605</t>
+          <t>Tovar uchun to'lov, h/f №8178 07.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6029,38 +6019,38 @@
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>4890000</v>
+        <v>7715000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3807 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2318</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6070,38 +6060,38 @@
       </c>
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="n">
-        <v>3586000</v>
+        <v>3377000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6769 31.08.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5123</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6111,38 +6101,38 @@
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>3558000</v>
+        <v>13042000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4932</t>
+          <t>Shartnoma №252/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6152,38 +6142,38 @@
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>1550000</v>
+        <v>11713000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6491</t>
+          <t>Shartnoma №284/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6191,35 +6181,40 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>4387000</v>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Oltin Vodiy Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Mahsuot uchun to'lov, shartnoma №46/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6227,40 +6222,40 @@
           <t>239</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>488000</v>
-      </c>
+      <c r="C149" s="2" t="n">
+        <v>1931000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>358326321</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000698368861001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2295 01.09.2026, QQS bilan</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №74/25</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6268,40 +6263,40 @@
           <t>240</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>409000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>9343000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6285 01.09.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №215/26</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6310,39 +6305,34 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>23348000</v>
+        <v>14900000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Shodlik Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>238372573</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3032)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000590147591001</t>
+          <t>16307000251139996417</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №94/26, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-3032 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6350,40 +6340,40 @@
           <t>242</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>455000</v>
-      </c>
+      <c r="C152" s="2" t="n">
+        <v>13145000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Gulshan Moy XK</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>332701087</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000399161879001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №241/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №190/26</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6391,40 +6381,40 @@
           <t>243</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>3105000</v>
-      </c>
+      <c r="C153" s="2" t="n">
+        <v>2306000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nihol Dori-Darmon MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>315021940</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000823760793001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №36/26, НДС 12%</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6432,40 +6422,40 @@
           <t>244</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>3214000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>2306000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Shartnoma №280/26 bo'yicha oldindan to'lov</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6473,40 +6463,40 @@
           <t>245</t>
         </is>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>603000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>5858000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>369409395</t>
+          <t>227959841</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000561422442001</t>
+          <t>20208000618750957001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8090</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №34/26</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6514,40 +6504,40 @@
           <t>246</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n">
-        <v>1931000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>4531000</v>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>270068797</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000136675861001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №76/25</t>
+          <t>SHARTNOMA №240/26 BO'YCHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6555,35 +6545,40 @@
           <t>247</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n">
-        <v>16907000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>5762000</v>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Oltin Vodiy Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Mahsulot uchun to'lov, shartn. №131/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6591,40 +6586,40 @@
           <t>248</t>
         </is>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>23499000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>4265000</v>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Kamalak Plastik AJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>235680841</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000008619306001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №86/26</t>
+          <t>Оплата за товар по счет-фактуре №3085 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6633,39 +6628,39 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>63045000</v>
+        <v>3297000</v>
       </c>
       <c r="D159" s="2" t="n"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>375469845</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000418813118001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTN. №275/26</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6673,40 +6668,40 @@
           <t>250</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>20986000</v>
-      </c>
+      <c r="C160" s="2" t="n">
+        <v>5880000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6864 08.09.2026, QQS BILAN</t>
+          <t>Tovarlar uchun to'lov h/f №5876</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6714,40 +6709,40 @@
           <t>251</t>
         </is>
       </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>389000</v>
-      </c>
+      <c r="C161" s="2" t="n">
+        <v>8928000</v>
+      </c>
+      <c r="D161" s="2" t="n"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Shartnoma №5/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №7308</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6756,39 +6751,39 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>21723000</v>
+        <v>19633000</v>
       </c>
       <c r="D162" s="2" t="n"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Omad Avto Ehtiyot AJ</t>
+          <t>Afrosiyob Moy AJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>286399411</t>
+          <t>383300872</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000988076583001</t>
+          <t>20208000184955062001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №47/26, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №2703</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6797,39 +6792,39 @@
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>31049000</v>
+        <v>21848000</v>
       </c>
       <c r="D163" s="2" t="n"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>336433225</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000853008516001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №8199</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №106/26</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6837,40 +6832,40 @@
           <t>254</t>
         </is>
       </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n">
-        <v>2740000</v>
-      </c>
+      <c r="C164" s="2" t="n">
+        <v>28595000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Shartnoma №2/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №4463</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6880,38 +6875,38 @@
       </c>
       <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="n">
-        <v>1631000</v>
+        <v>8703000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Denov Plastik MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>280939580</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000543058880001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5912 09.09.2026, QQS bilan</t>
+          <t>Shartnoma №192/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6919,40 +6914,40 @@
           <t>256</t>
         </is>
       </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>555000</v>
-      </c>
+      <c r="C166" s="2" t="n">
+        <v>6725000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>241356725</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000380253078001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6026 за поставленный товар</t>
+          <t>Оплата за товары согласно с/ф №309</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6961,34 +6956,39 @@
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>14900000</v>
+        <v>20284000</v>
       </c>
       <c r="D167" s="2" t="n"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3032)</t>
+          <t>Navoiy Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>16307000251139996417</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3032 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №191/26</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6998,38 +6998,38 @@
       </c>
       <c r="C168" s="2" t="n"/>
       <c r="D168" s="2" t="n">
-        <v>4754000</v>
+        <v>24327000</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №242/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №74/26 от 23.09.2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7039,38 +7039,38 @@
       </c>
       <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="n">
-        <v>1214000</v>
+        <v>8959000</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №142/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №62/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7080,21 +7080,21 @@
       </c>
       <c r="C170" s="2" t="n"/>
       <c r="D170" s="2" t="n">
-        <v>1006000</v>
+        <v>3381000</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Barakali Polimer MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>347370934</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>20208000473996710001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7104,14 +7104,14 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Shartnoma №121/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №86/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7119,40 +7119,40 @@
           <t>261</t>
         </is>
       </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>739000</v>
-      </c>
+      <c r="C171" s="2" t="n">
+        <v>33053000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Afrosiyob Moy AJ</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>383300872</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000184955062001</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8551 14.09.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №3660</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7162,21 +7162,21 @@
       </c>
       <c r="C172" s="2" t="n"/>
       <c r="D172" s="2" t="n">
-        <v>693000</v>
+        <v>8053000</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Shodlik Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>330013963</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000066780292001</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7186,14 +7186,14 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7567 за поставленный товар</t>
+          <t>Shartnoma №156/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7203,38 +7203,38 @@
       </c>
       <c r="C173" s="2" t="n"/>
       <c r="D173" s="2" t="n">
-        <v>684000</v>
+        <v>3258000</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7381 14.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №185/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7242,40 +7242,40 @@
           <t>264</t>
         </is>
       </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>494000</v>
-      </c>
+      <c r="C174" s="2" t="n">
+        <v>1207000</v>
+      </c>
+      <c r="D174" s="2" t="n"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Qarshi Non MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>376646629</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>20208000922620047001</t>
+          <t>20208000944796837001</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №3458</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7285,38 +7285,38 @@
       </c>
       <c r="C175" s="2" t="n"/>
       <c r="D175" s="2" t="n">
-        <v>423000</v>
+        <v>3996000</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Bog'ishamol Metall Servis XK</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>369409395</t>
+          <t>293958025</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>20208000561422442001</t>
+          <t>20208000305888016001</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №6733 ОТ 14.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Shartnoma №120/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7325,39 +7325,39 @@
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>24073000</v>
+        <v>8242000</v>
       </c>
       <c r="D176" s="2" t="n"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Kamalak Plastik AJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>235680841</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>20208000008619306001</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №110/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №278/26</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -7367,38 +7367,38 @@
       </c>
       <c r="C177" s="2" t="n"/>
       <c r="D177" s="2" t="n">
-        <v>897000</v>
+        <v>20028000</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Kamalak Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>288948459</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000029421730001</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Shartnoma №110/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, h/f №5935 29.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -7408,38 +7408,38 @@
       </c>
       <c r="C178" s="2" t="n"/>
       <c r="D178" s="2" t="n">
-        <v>503000</v>
+        <v>13678000</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №260 15.09.2026, QQS bilan</t>
+          <t>Shartnoma №176/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -7447,40 +7447,40 @@
           <t>269</t>
         </is>
       </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>499000</v>
-      </c>
+      <c r="C179" s="2" t="n">
+        <v>13691000</v>
+      </c>
+      <c r="D179" s="2" t="n"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
+          <t>Mehnat Savdo MChJ</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>359135425</t>
+          <t>337257395</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>20208000343675517001</t>
+          <t>20208000014759122001</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №138 15.09.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №246/26</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7490,38 +7490,38 @@
       </c>
       <c r="C180" s="2" t="n"/>
       <c r="D180" s="2" t="n">
-        <v>753000</v>
+        <v>3401000</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Olmaliq Agro MChJ</t>
+          <t>Oltin Vodiy Moy MChJ</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>331889484</t>
+          <t>313542553</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>20208000990294217001</t>
+          <t>20208000367551758001</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №77/26, QQS 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8047 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -7530,39 +7530,34 @@
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>2306000</v>
+        <v>300000</v>
       </c>
       <c r="D181" s="2" t="n"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ijtimoiy soliq</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -7571,832 +7566,58 @@
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>2306000</v>
+        <v>32581000</v>
       </c>
       <c r="D182" s="2" t="n"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>397984978</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000768607374001</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LO, SHARTN. №274/26</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="n">
-        <v>22538000</v>
-      </c>
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Shodlik Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>238372573</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000590147591001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №67/26</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="n">
+        <v>862181000</v>
+      </c>
+      <c r="D183" s="4" t="n">
+        <v>867481000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="n"/>
-      <c r="D184" s="2" t="n">
-        <v>2650000</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1346 17.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="n"/>
-      <c r="D185" s="2" t="n">
-        <v>2744000</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5326</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="n"/>
-      <c r="D186" s="2" t="n">
-        <v>525000</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2572 21.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="n"/>
-      <c r="D187" s="2" t="n">
-        <v>193568000</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>369409395</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>20208000561422442001</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №175/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="n"/>
-      <c r="D188" s="2" t="n">
-        <v>2144000</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Shartnoma №129/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="n">
-        <v>18460000</v>
-      </c>
-      <c r="D189" s="2" t="n"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Kamalak Plastik AJ</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>235680841</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>20208000008619306001</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №206/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="n">
-        <v>1207000</v>
-      </c>
-      <c r="D190" s="2" t="n"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>20208000408297732001</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Elektr energiyasi uchun to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="n">
-        <v>3180000</v>
-      </c>
-      <c r="D191" s="2" t="n"/>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>QQS avgust 2026 uchun</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="n"/>
-      <c r="D192" s="2" t="n">
-        <v>2739000</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3018</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="n"/>
-      <c r="D193" s="2" t="n">
-        <v>5234000</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6002</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="n"/>
-      <c r="D194" s="2" t="n">
-        <v>2166000</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Shartnoma №231/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="n"/>
-      <c r="D195" s="2" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Olmaliq Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>331889484</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>20208000990294217001</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>Shartnoma №235/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="n"/>
-      <c r="D196" s="2" t="n">
-        <v>1122000</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, h/f №7642 28.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="n"/>
-      <c r="D197" s="2" t="n">
-        <v>1019000</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №572</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="n"/>
-      <c r="D198" s="2" t="n">
-        <v>921000</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Olmaliq Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>331889484</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>20208000990294217001</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisb-faktura №8262 28.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="n"/>
-      <c r="D199" s="2" t="n">
-        <v>563000</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>Shartnoma №264/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="n"/>
-      <c r="D200" s="2" t="n">
-        <v>652000</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Marg'ilon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>359135425</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>20208000343675517001</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №73/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D201" s="2" t="n"/>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Oqsaroy Bank ATB</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="n">
-        <v>861952000</v>
-      </c>
-      <c r="D202" s="4" t="n">
-        <v>867252000</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C203" s="4" t="n">
+      <c r="C184" s="4" t="n">
         <v>75600000</v>
       </c>
-      <c r="D203" s="4" t="n"/>
+      <c r="D184" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
